--- a/data/availability/projects/emaar-misr/cairo-gate.xlsx
+++ b/data/availability/projects/emaar-misr/cairo-gate.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for cairo-gate</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1209,7 +1219,6 @@
       <c r="G2" t="n">
         <v>120</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1220,7 +1229,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1266,7 +1275,6 @@
       <c r="G3" t="n">
         <v>120</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1277,7 +1285,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1323,7 +1331,6 @@
       <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1334,7 +1341,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1380,7 +1387,6 @@
       <c r="G5" t="n">
         <v>300.6</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1391,7 +1397,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1437,7 +1443,6 @@
       <c r="G6" t="n">
         <v>300.6</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1448,7 +1453,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1494,7 +1499,6 @@
       <c r="G7" t="n">
         <v>300.6</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1505,7 +1509,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1551,7 +1555,6 @@
       <c r="G8" t="n">
         <v>300.6</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1562,7 +1565,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1608,7 +1611,6 @@
       <c r="G9" t="n">
         <v>490.9</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1619,7 +1621,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1665,7 +1667,6 @@
       <c r="G10" t="n">
         <v>481.5</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1676,7 +1677,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1722,7 +1723,6 @@
       <c r="G11" t="n">
         <v>481.5</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1779,7 +1779,6 @@
       <c r="G12" t="n">
         <v>481.5</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1790,7 +1789,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1836,7 +1835,6 @@
       <c r="G13" t="n">
         <v>447.3</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1847,7 +1845,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1893,7 +1891,6 @@
       <c r="G14" t="n">
         <v>540.3</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1904,7 +1901,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1950,7 +1947,6 @@
       <c r="G15" t="n">
         <v>474</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1961,7 +1957,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2007,7 +2003,6 @@
       <c r="G16" t="n">
         <v>703.3</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2018,7 +2013,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2064,7 +2059,6 @@
       <c r="G17" t="n">
         <v>735</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2075,7 +2069,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2121,7 +2115,6 @@
       <c r="G18" t="n">
         <v>640.9</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2132,7 +2125,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2178,7 +2171,6 @@
       <c r="G19" t="n">
         <v>401.4</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2189,7 +2181,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2235,7 +2227,6 @@
       <c r="G20" t="n">
         <v>436.4</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2246,7 +2237,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2292,7 +2283,6 @@
       <c r="G21" t="n">
         <v>552.7</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2303,7 +2293,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2349,7 +2339,6 @@
       <c r="G22" t="n">
         <v>325.1</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2360,7 +2349,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2406,7 +2395,6 @@
       <c r="G23" t="n">
         <v>411.2</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2417,7 +2405,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2463,7 +2451,6 @@
       <c r="G24" t="n">
         <v>403.2</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2474,7 +2461,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2520,7 +2507,6 @@
       <c r="G25" t="n">
         <v>414.2</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2531,7 +2517,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2577,7 +2563,6 @@
       <c r="G26" t="n">
         <v>445.4</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2588,7 +2573,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2634,7 +2619,6 @@
       <c r="G27" t="n">
         <v>381</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2645,7 +2629,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2691,7 +2675,6 @@
       <c r="G28" t="n">
         <v>338.7</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2702,7 +2685,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2748,7 +2731,6 @@
       <c r="G29" t="n">
         <v>366.8</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2759,7 +2741,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2805,7 +2787,6 @@
       <c r="G30" t="n">
         <v>435.1</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2816,7 +2797,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2862,7 +2843,6 @@
       <c r="G31" t="n">
         <v>444.4</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2873,7 +2853,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2919,7 +2899,6 @@
       <c r="G32" t="n">
         <v>502.7</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2930,7 +2909,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2976,7 +2955,6 @@
       <c r="G33" t="n">
         <v>435.7</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2987,7 +2965,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3033,7 +3011,6 @@
       <c r="G34" t="n">
         <v>407.1</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3044,7 +3021,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3090,7 +3067,6 @@
       <c r="G35" t="n">
         <v>381.7</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3101,7 +3077,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3147,7 +3123,6 @@
       <c r="G36" t="n">
         <v>342.9</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3158,7 +3133,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3204,7 +3179,6 @@
       <c r="G37" t="n">
         <v>457.1</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3215,7 +3189,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3261,7 +3235,6 @@
       <c r="G38" t="n">
         <v>448.8</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3272,7 +3245,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3318,7 +3291,6 @@
       <c r="G39" t="n">
         <v>334.9</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3329,7 +3301,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3375,7 +3347,6 @@
       <c r="G40" t="n">
         <v>470.4</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3386,7 +3357,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3432,7 +3403,6 @@
       <c r="G41" t="n">
         <v>458.3</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3443,7 +3413,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3489,7 +3459,6 @@
       <c r="G42" t="n">
         <v>418.7</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3500,7 +3469,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3546,7 +3515,6 @@
       <c r="G43" t="n">
         <v>401.9</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3557,7 +3525,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3603,7 +3571,6 @@
       <c r="G44" t="n">
         <v>536.5</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3614,7 +3581,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>31/05/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3660,7 +3627,6 @@
       <c r="G45" t="n">
         <v>409</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3671,7 +3637,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3717,7 +3683,6 @@
       <c r="G46" t="n">
         <v>409.6</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3728,7 +3693,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3774,7 +3739,6 @@
       <c r="G47" t="n">
         <v>97.7</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3785,7 +3749,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3831,7 +3795,6 @@
       <c r="G48" t="n">
         <v>997.5</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3842,7 +3805,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3888,7 +3851,6 @@
       <c r="G49" t="n">
         <v>892.5</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3899,7 +3861,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3945,7 +3907,6 @@
       <c r="G50" t="n">
         <v>388.5</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3956,7 +3917,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4002,7 +3963,6 @@
       <c r="G51" t="n">
         <v>380.6</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4013,7 +3973,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4059,7 +4019,6 @@
       <c r="G52" t="n">
         <v>382.9</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4070,7 +4029,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4116,7 +4075,6 @@
       <c r="G53" t="n">
         <v>382.9</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4127,7 +4085,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4173,7 +4131,6 @@
       <c r="G54" t="n">
         <v>464.1</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4184,7 +4141,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4230,7 +4187,6 @@
       <c r="G55" t="n">
         <v>401</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4241,7 +4197,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4287,7 +4243,6 @@
       <c r="G56" t="n">
         <v>421</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4298,7 +4253,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4344,7 +4299,6 @@
       <c r="G57" t="n">
         <v>380.9</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4355,7 +4309,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4401,7 +4355,6 @@
       <c r="G58" t="n">
         <v>396.2</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4412,7 +4365,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4458,7 +4411,6 @@
       <c r="G59" t="n">
         <v>413.1</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4469,7 +4421,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4515,7 +4467,6 @@
       <c r="G60" t="n">
         <v>476.1</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4526,7 +4477,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4572,7 +4523,6 @@
       <c r="G61" t="n">
         <v>510.7</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4583,7 +4533,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4629,7 +4579,6 @@
       <c r="G62" t="n">
         <v>510.7</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4640,7 +4589,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4686,7 +4635,6 @@
       <c r="G63" t="n">
         <v>542.7</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4697,7 +4645,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4743,7 +4691,6 @@
       <c r="G64" t="n">
         <v>383</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4754,7 +4701,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4800,7 +4747,6 @@
       <c r="G65" t="n">
         <v>385.3</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4811,7 +4757,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4857,7 +4803,6 @@
       <c r="G66" t="n">
         <v>382</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4868,7 +4813,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4914,7 +4859,6 @@
       <c r="G67" t="n">
         <v>401.9</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4925,7 +4869,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4971,7 +4915,6 @@
       <c r="G68" t="n">
         <v>637.8</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4982,7 +4925,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5028,7 +4971,6 @@
       <c r="G69" t="n">
         <v>95.8</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5039,7 +4981,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5085,7 +5027,6 @@
       <c r="G70" t="n">
         <v>105.4</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5096,7 +5037,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5142,7 +5083,6 @@
       <c r="G71" t="n">
         <v>398.7</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5153,7 +5093,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5199,7 +5139,6 @@
       <c r="G72" t="n">
         <v>409</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5210,7 +5149,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>29/02/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5256,7 +5195,6 @@
       <c r="G73" t="n">
         <v>371.6</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5267,7 +5205,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5313,7 +5251,6 @@
       <c r="G74" t="n">
         <v>371.6</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5324,7 +5261,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5370,7 +5307,6 @@
       <c r="G75" t="n">
         <v>371.6</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5381,7 +5317,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5427,7 +5363,6 @@
       <c r="G76" t="n">
         <v>371.6</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5438,7 +5373,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5484,7 +5419,6 @@
       <c r="G77" t="n">
         <v>382.1</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5495,7 +5429,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5541,7 +5475,6 @@
       <c r="G78" t="n">
         <v>120</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5552,7 +5485,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5598,7 +5531,6 @@
       <c r="G79" t="n">
         <v>120</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5609,7 +5541,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5655,7 +5587,6 @@
       <c r="G80" t="n">
         <v>120</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5666,7 +5597,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5712,7 +5643,6 @@
       <c r="G81" t="n">
         <v>120</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5723,7 +5653,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5769,7 +5699,6 @@
       <c r="G82" t="n">
         <v>120</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5780,7 +5709,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5826,7 +5755,6 @@
       <c r="G83" t="n">
         <v>120</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5837,7 +5765,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5883,7 +5811,6 @@
       <c r="G84" t="n">
         <v>120</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5894,7 +5821,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5940,7 +5867,6 @@
       <c r="G85" t="n">
         <v>120</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5951,7 +5877,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5997,7 +5923,6 @@
       <c r="G86" t="n">
         <v>120</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6008,7 +5933,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6054,7 +5979,6 @@
       <c r="G87" t="n">
         <v>120</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6065,7 +5989,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6111,7 +6035,6 @@
       <c r="G88" t="n">
         <v>120</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6122,7 +6045,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6168,7 +6091,6 @@
       <c r="G89" t="n">
         <v>120</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6179,7 +6101,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6225,7 +6147,6 @@
       <c r="G90" t="n">
         <v>120</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6236,7 +6157,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6282,7 +6203,6 @@
       <c r="G91" t="n">
         <v>120</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6293,7 +6213,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6339,7 +6259,6 @@
       <c r="G92" t="n">
         <v>120</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6350,7 +6269,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6396,7 +6315,6 @@
       <c r="G93" t="n">
         <v>120</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -6407,7 +6325,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>30/06/2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
